--- a/artfynd/A 63146-2025 artfynd.xlsx
+++ b/artfynd/A 63146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4959498</v>
+        <v>66198135</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>F.d. Eliseberg, Ramnäs sn, Vstm</t>
+          <t>F d Eliseberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564151.2431138299</v>
+        <v>564117</v>
       </c>
       <c r="R2" t="n">
-        <v>6629650.877014432</v>
+        <v>6629756</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På samma träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,38 +769,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Moränås, lövdominerad skog</t>
+          <t>Örtrik blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4959496</v>
+        <v>4959495</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564143.1792656542</v>
+        <v>564128</v>
       </c>
       <c r="R3" t="n">
-        <v>6629679.930859922</v>
+        <v>6629739</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,21 +866,11 @@
           <t>2012-05-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +882,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Moränkulle, gles lövdominerad skog.</t>
+          <t>Moränkulle, gles lövdominerad skog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4959499</v>
+        <v>4959496</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564163.9128901912</v>
+        <v>564143</v>
       </c>
       <c r="R4" t="n">
-        <v>6629617.875749168</v>
+        <v>6629680</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,21 +968,11 @@
           <t>2012-05-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-05-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +984,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Moränås, lövdominerad skog.</t>
+          <t>Moränkulle, gles lövdominerad skog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66197831</v>
+        <v>4959497</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,26 +1031,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>F d Eliseberg, Vstm</t>
+          <t>F.d. Eliseberg, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564042.1406794229</v>
+        <v>564151</v>
       </c>
       <c r="R5" t="n">
-        <v>6629896.625946561</v>
+        <v>6629651</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,22 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,33 +1086,28 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Moränkulle, gles lövdominerad skog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66198547</v>
+        <v>4959499</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,48 +1115,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>F d Eliseberg, Vstm</t>
+          <t>F.d. Eliseberg, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564161.3932851113</v>
+        <v>564164</v>
       </c>
       <c r="R6" t="n">
-        <v>6629647.025466543</v>
+        <v>6629618</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,22 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,33 +1188,28 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Örtrik blandskog</t>
+          <t>Moränås, lövdominerad skog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66198470</v>
+        <v>66197831</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1236,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564138.1736467858</v>
+        <v>564042</v>
       </c>
       <c r="R7" t="n">
-        <v>6629677.831240962</v>
+        <v>6629897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,21 +1281,11 @@
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1297,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Örtrik blandskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1398,15 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66198497</v>
+        <v>66198470</v>
       </c>
       <c r="B8" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1414,33 +1326,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1449,13 +1353,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564155.1018232189</v>
+        <v>564138</v>
       </c>
       <c r="R8" t="n">
-        <v>6629661.010120152</v>
+        <v>6629678</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,19 +1386,9 @@
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,15 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66198564</v>
+        <v>66198529</v>
       </c>
       <c r="B9" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,33 +1431,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1577,13 +1458,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564165.9464155858</v>
+        <v>564153</v>
       </c>
       <c r="R9" t="n">
-        <v>6629616.90416413</v>
+        <v>6629648</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,19 +1491,9 @@
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,15 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66198529</v>
+        <v>66197959</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,26 +1536,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1697,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564153.3113335113</v>
+        <v>564083</v>
       </c>
       <c r="R10" t="n">
-        <v>6629647.892716506</v>
+        <v>6629836</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1730,21 +1608,11 @@
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1756,7 +1624,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Örtrik blandskog</t>
+          <t>Blandskog asp, gran, björk</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1771,6 +1639,345 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>66198497</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>F d Eliseberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564155</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6629661</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-06-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-06-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrik blandskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>66198547</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>F d Eliseberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564161</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6629647</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-06-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-06-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Örtrik blandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>66198564</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>F d Eliseberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6629617</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-06-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-06-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Örtrik blandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63146-2025 artfynd.xlsx
+++ b/artfynd/A 63146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66197831</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66197959</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66198135</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4959495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4959496</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4959497</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4959499</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66198470</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66198529</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66198497</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66198547</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,8 +2038,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66198564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>